--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-03-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%91%d7%91%d7%94-jean/</v>
+        <v>https://yosmusic.com/%d7%92%d7%95%d7%a8%d7%99%d7%9c%d7%96-the-mountain/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זה אלבומה השני של יבבה (Yebba) הזמרת-יוצרת, ילידת ארקנסו המוכרת מהשיר הנפלא October Sky.  זהו  אוסף שירים בעל ניחוח פולקי עם השפעות גוספל – יצירה בוגרת יותר בסגנון פופ עכשווי שמגיעה אחרי אלבום הבכורה שלה Dawn. האלבום נקרא על שם</v>
+        <v>בשלב מסוים במהלך השיר Orange County הבנתי שאני לא רק נהנה מהאלבום The Mountain, אלא שאני גם קצת המום מהייחוד שלו. לאורך 15 שירים מאזינים לתערובת מסחררת של מצבי רוח, סגנונות, תרבויות, שפות ותקופות The Mountain הוא אלבום האולפן התשיעי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יבבה Jean</v>
+        <v>גורילז The Mountain</v>
       </c>
     </row>
   </sheetData>
